--- a/SWR302/assignment/SWR302_Assignment_TaskList_TeamX.xlsx
+++ b/SWR302/assignment/SWR302_Assignment_TaskList_TeamX.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10308"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Snake\FU\Teach\Material\SWR302\Assignment\Reference\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/fptu/SWR302/assignment/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82E428D2-FB65-B242-9F67-4670AA7E9ABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9192"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="23040" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="53">
   <si>
     <t>Table of Contents</t>
   </si>
@@ -180,12 +181,15 @@
   </si>
   <si>
     <t>6. Limitations and Exclusions</t>
+  </si>
+  <si>
+    <t>Phạm Tuấn Anh</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -555,15 +559,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B52"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="35.77734375" customWidth="1"/>
+    <col min="1" max="1" width="35.83203125" customWidth="1"/>
     <col min="2" max="2" width="37" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="21" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -571,307 +575,317 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="6"/>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="2"/>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="6"/>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>47</v>
       </c>
       <c r="B6" s="6"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>48</v>
       </c>
       <c r="B7" s="6"/>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>49</v>
       </c>
       <c r="B8" s="6"/>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B9" s="6"/>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B9" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>51</v>
       </c>
       <c r="B10" s="6"/>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B11" s="2"/>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="6"/>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B12" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B13" s="6"/>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B14" s="2"/>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B15" s="6"/>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B16" s="2"/>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="6"/>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B17" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B18" s="6"/>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B19" s="6"/>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B20" s="2"/>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>15</v>
       </c>
       <c r="B21" s="2"/>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B22" s="6"/>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B22" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>17</v>
       </c>
       <c r="B23" s="6"/>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>18</v>
       </c>
       <c r="B24" s="6"/>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>19</v>
       </c>
       <c r="B25" s="6"/>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>20</v>
       </c>
       <c r="B26" s="2"/>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B27" s="6"/>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>22</v>
       </c>
       <c r="B28" s="6"/>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>23</v>
       </c>
       <c r="B29" s="6"/>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>24</v>
       </c>
       <c r="B30" s="6"/>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B31" s="2"/>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>26</v>
       </c>
       <c r="B32" s="6"/>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>27</v>
       </c>
       <c r="B33" s="6"/>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
         <v>28</v>
       </c>
       <c r="B34" s="2"/>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
         <v>44</v>
       </c>
       <c r="B35" s="6"/>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
         <v>45</v>
       </c>
       <c r="B36" s="6"/>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
         <v>29</v>
       </c>
       <c r="B37" s="2"/>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B38" s="2"/>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B39" s="6"/>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B39" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
         <v>32</v>
       </c>
       <c r="B40" s="6"/>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
         <v>33</v>
       </c>
       <c r="B41" s="6"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
         <v>34</v>
       </c>
       <c r="B42" s="6"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B43" s="2"/>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
         <v>36</v>
       </c>
       <c r="B44" s="6"/>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B45" s="6"/>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
         <v>38</v>
       </c>
       <c r="B46" s="6"/>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
         <v>39</v>
       </c>
       <c r="B47" s="6"/>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
         <v>40</v>
       </c>
       <c r="B48" s="6"/>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
         <v>41</v>
       </c>
       <c r="B49" s="6"/>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
         <v>42</v>
       </c>
       <c r="B50" s="6"/>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
         <v>43</v>
       </c>
       <c r="B51" s="6"/>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" s="1"/>
     </row>
   </sheetData>
